--- a/JAMS/Results Analysis/tech_potential.xlsx
+++ b/JAMS/Results Analysis/tech_potential.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DESKTOP\Desktop\Github\Raster_PV_Poten\JAMS\Results Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sidus\Desktop\GRI Github\Raster_PV_Poten\JAMS\Results Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC90BE4A-6BD4-4147-8EF3-9A2D0BFB05F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDEBD796-2EB9-4A0E-B3BB-965C869E74D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" activeTab="1" xr2:uid="{B9C9FEB6-836D-4C74-BC39-A2355B1940F7}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{B9C9FEB6-836D-4C74-BC39-A2355B1940F7}"/>
   </bookViews>
   <sheets>
     <sheet name="데이터" sheetId="1" r:id="rId1"/>
@@ -220,11 +220,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -560,9 +561,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B573BC60-FE83-40A1-9832-1B173CCAE4BF}">
   <dimension ref="A1:E63"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -579,8 +580,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -589,15 +590,15 @@
       <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="1">
-        <v>2618545.3222884946</v>
+      <c r="D2" s="2">
+        <v>2557656.3699444849</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -606,15 +607,15 @@
       <c r="C3" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="1">
-        <v>2008131.6258640192</v>
+      <c r="D3" s="2">
+        <v>1963509.3577575809</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -623,15 +624,15 @@
       <c r="C4" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="1">
-        <v>29727345.655073699</v>
+      <c r="D4" s="2">
+        <v>27464732.97555593</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -640,15 +641,15 @@
       <c r="C5" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="1">
-        <v>1921398.9363479791</v>
+      <c r="D5" s="2">
+        <v>1839270.797627446</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -657,15 +658,15 @@
       <c r="C6" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="1">
-        <v>1096651.0761127521</v>
+      <c r="D6" s="2">
+        <v>1081076.9581642181</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -674,15 +675,15 @@
       <c r="C7" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="1">
-        <v>1530036.7906580151</v>
+      <c r="D7" s="2">
+        <v>1504912.482897728</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -691,15 +692,15 @@
       <c r="C8" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="1">
-        <v>11920612.374376204</v>
+      <c r="D8" s="2">
+        <v>11512379.36300838</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -708,15 +709,15 @@
       <c r="C9" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="1">
-        <v>2599134.9648780758</v>
+      <c r="D9" s="2">
+        <v>2563385.2098970702</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -725,15 +726,15 @@
       <c r="C10" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="1">
-        <v>7869990.0985480109</v>
+      <c r="D10" s="2">
+        <v>7628319.1523490958</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -742,15 +743,15 @@
       <c r="C11" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="1">
-        <v>1534370.4773225782</v>
+      <c r="D11" s="2">
+        <v>1523450.64263628</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -759,15 +760,15 @@
       <c r="C12" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="1">
-        <v>1865303.043499928</v>
+      <c r="D12" s="2">
+        <v>1832963.5794725739</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -776,15 +777,15 @@
       <c r="C13" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="1">
-        <v>3107446.0949707306</v>
+      <c r="D13" s="2">
+        <v>3043595.872125661</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -793,15 +794,15 @@
       <c r="C14" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="1">
-        <v>30167437.387053836</v>
+      <c r="D14" s="2">
+        <v>26673303.184836831</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -810,15 +811,15 @@
       <c r="C15" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="1">
-        <v>26031171.836254764</v>
+      <c r="D15" s="2">
+        <v>25216746.597958948</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -827,15 +828,15 @@
       <c r="C16" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="1">
-        <v>25835380.798853062</v>
+      <c r="D16" s="2">
+        <v>24436481.808469661</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -844,15 +845,15 @@
       <c r="C17" t="s">
         <v>7</v>
       </c>
-      <c r="D17" s="1">
-        <v>15914053.227327503</v>
+      <c r="D17" s="2">
+        <v>14604364.51658274</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B18" s="1" t="s">
@@ -861,15 +862,15 @@
       <c r="C18" t="s">
         <v>7</v>
       </c>
-      <c r="D18" s="1">
-        <v>42497399.980089523</v>
+      <c r="D18" s="2">
+        <v>41399920.525362223</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B19" s="1" t="s">
@@ -878,15 +879,15 @@
       <c r="C19" t="s">
         <v>7</v>
       </c>
-      <c r="D19" s="1">
-        <v>10201077.628245702</v>
+      <c r="D19" s="2">
+        <v>9876115.8785107657</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B20" s="1" t="s">
@@ -895,15 +896,15 @@
       <c r="C20" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="1">
-        <v>11041067.980602838</v>
+      <c r="D20" s="2">
+        <v>10587712.4479456</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B21" s="1" t="s">
@@ -912,15 +913,15 @@
       <c r="C21" t="s">
         <v>7</v>
       </c>
-      <c r="D21" s="1">
-        <v>20892366.657576159</v>
+      <c r="D21" s="2">
+        <v>19704021.114184462</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B22" s="1" t="s">
@@ -929,15 +930,15 @@
       <c r="C22" t="s">
         <v>7</v>
       </c>
-      <c r="D22" s="1">
-        <v>27064072.604449451</v>
+      <c r="D22" s="2">
+        <v>26013921.850878488</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -946,15 +947,15 @@
       <c r="C23" t="s">
         <v>7</v>
       </c>
-      <c r="D23" s="1">
-        <v>19062867.652953368</v>
+      <c r="D23" s="2">
+        <v>17169617.637996271</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B24" s="1" t="s">
@@ -963,15 +964,15 @@
       <c r="C24" t="s">
         <v>7</v>
       </c>
-      <c r="D24" s="1">
-        <v>9501047.796062652</v>
+      <c r="D24" s="2">
+        <v>9026633.4806367233</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B25" s="1" t="s">
@@ -980,15 +981,15 @@
       <c r="C25" t="s">
         <v>7</v>
       </c>
-      <c r="D25" s="1">
-        <v>17832105.648064818</v>
+      <c r="D25" s="2">
+        <v>17100495.372796919</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
         <v>32</v>
       </c>
       <c r="B26" s="1" t="s">
@@ -997,15 +998,15 @@
       <c r="C26" t="s">
         <v>7</v>
       </c>
-      <c r="D26" s="1">
-        <v>6972260.7842857866</v>
+      <c r="D26" s="2">
+        <v>6474247.526741581</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B27" s="1" t="s">
@@ -1014,15 +1015,15 @@
       <c r="C27" t="s">
         <v>7</v>
       </c>
-      <c r="D27" s="1">
-        <v>5057459.0394964684</v>
+      <c r="D27" s="2">
+        <v>4847745.5816820525</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B28" s="1" t="s">
@@ -1031,15 +1032,15 @@
       <c r="C28" t="s">
         <v>7</v>
       </c>
-      <c r="D28" s="1">
-        <v>1905412.8368749646</v>
+      <c r="D28" s="2">
+        <v>1879489.8660602709</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
         <v>35</v>
       </c>
       <c r="B29" s="1" t="s">
@@ -1048,15 +1049,15 @@
       <c r="C29" t="s">
         <v>7</v>
       </c>
-      <c r="D29" s="1">
-        <v>3198374.0243559103</v>
+      <c r="D29" s="2">
+        <v>3176203.833221327</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B30" s="1" t="s">
@@ -1065,15 +1066,15 @@
       <c r="C30" t="s">
         <v>7</v>
       </c>
-      <c r="D30" s="1">
-        <v>7893854.0490570413</v>
+      <c r="D30" s="2">
+        <v>7758626.0567768207</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B31" s="1" t="s">
@@ -1082,15 +1083,15 @@
       <c r="C31" t="s">
         <v>7</v>
       </c>
-      <c r="D31" s="1">
-        <v>13407680.359273193</v>
+      <c r="D31" s="2">
+        <v>12810557.243432891</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B32" s="1" t="s">
@@ -1099,15 +1100,15 @@
       <c r="C32" t="s">
         <v>7</v>
       </c>
-      <c r="D32" s="1">
-        <v>22696246.930279989</v>
+      <c r="D32" s="2">
+        <v>22229564.728966281</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B33" s="1" t="s">
@@ -1116,15 +1117,15 @@
       <c r="C33" t="s">
         <v>39</v>
       </c>
-      <c r="D33" s="1">
-        <v>331828.14917516755</v>
+      <c r="D33" s="2">
+        <v>331710.07764768432</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B34" s="1" t="s">
@@ -1133,15 +1134,15 @@
       <c r="C34" t="s">
         <v>39</v>
       </c>
-      <c r="D34" s="1">
-        <v>211133.03611803058</v>
+      <c r="D34" s="2">
+        <v>211112.86736345131</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B35" s="1" t="s">
@@ -1150,15 +1151,15 @@
       <c r="C35" t="s">
         <v>39</v>
       </c>
-      <c r="D35" s="1">
-        <v>1518054.8773636702</v>
+      <c r="D35" s="2">
+        <v>1494185.068305016</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B36" s="1" t="s">
@@ -1167,15 +1168,15 @@
       <c r="C36" t="s">
         <v>39</v>
       </c>
-      <c r="D36" s="1">
-        <v>160613.93903636906</v>
+      <c r="D36" s="2">
+        <v>160359.3819413184</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B37" s="1" t="s">
@@ -1184,15 +1185,15 @@
       <c r="C37" t="s">
         <v>39</v>
       </c>
-      <c r="D37" s="1">
-        <v>92056.666982650699</v>
+      <c r="D37" s="2">
+        <v>92043.358213901462</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B38" s="1" t="s">
@@ -1201,15 +1202,15 @@
       <c r="C38" t="s">
         <v>39</v>
       </c>
-      <c r="D38" s="1">
-        <v>164406.88190126367</v>
+      <c r="D38" s="2">
+        <v>164327.4628033631</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B39" s="1" t="s">
@@ -1218,15 +1219,15 @@
       <c r="C39" t="s">
         <v>39</v>
       </c>
-      <c r="D39" s="1">
-        <v>978488.34124946373</v>
+      <c r="D39" s="2">
+        <v>977729.48949575878</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B40" s="1" t="s">
@@ -1235,15 +1236,15 @@
       <c r="C40" t="s">
         <v>39</v>
       </c>
-      <c r="D40" s="1">
-        <v>254843.57577896057</v>
+      <c r="D40" s="2">
+        <v>254830.2714781758</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B41" s="1" t="s">
@@ -1252,15 +1253,15 @@
       <c r="C41" t="s">
         <v>39</v>
       </c>
-      <c r="D41" s="1">
-        <v>798510.64539670653</v>
+      <c r="D41" s="2">
+        <v>798349.59670543834</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B42" s="1" t="s">
@@ -1269,15 +1270,15 @@
       <c r="C42" t="s">
         <v>39</v>
       </c>
-      <c r="D42" s="1">
-        <v>203224.9084978101</v>
+      <c r="D42" s="2">
+        <v>203211.59323406289</v>
       </c>
       <c r="E42" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B43" s="1" t="s">
@@ -1286,15 +1287,15 @@
       <c r="C43" t="s">
         <v>39</v>
       </c>
-      <c r="D43" s="1">
-        <v>140606.11464595757</v>
+      <c r="D43" s="2">
+        <v>140486.10806131409</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B44" s="1" t="s">
@@ -1303,15 +1304,15 @@
       <c r="C44" t="s">
         <v>39</v>
       </c>
-      <c r="D44" s="1">
-        <v>339334.12628841383</v>
+      <c r="D44" s="2">
+        <v>339174.89427852881</v>
       </c>
       <c r="E44" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B45" s="1" t="s">
@@ -1320,15 +1321,15 @@
       <c r="C45" t="s">
         <v>39</v>
       </c>
-      <c r="D45" s="1">
-        <v>1187899.5447406741</v>
+      <c r="D45" s="2">
+        <v>1185793.261952877</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B46" s="1" t="s">
@@ -1337,15 +1338,15 @@
       <c r="C46" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="1">
-        <v>1024536.2307333954</v>
+      <c r="D46" s="2">
+        <v>1023501.10076761</v>
       </c>
       <c r="E46" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B47" s="1" t="s">
@@ -1354,15 +1355,15 @@
       <c r="C47" t="s">
         <v>39</v>
       </c>
-      <c r="D47" s="1">
-        <v>1018955.5110178095</v>
+      <c r="D47" s="2">
+        <v>993106.54226113623</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B48" s="1" t="s">
@@ -1371,15 +1372,15 @@
       <c r="C48" t="s">
         <v>39</v>
       </c>
-      <c r="D48" s="1">
-        <v>1046281.6376352301</v>
+      <c r="D48" s="2">
+        <v>1044923.621275431</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B49" s="1" t="s">
@@ -1388,15 +1389,15 @@
       <c r="C49" t="s">
         <v>39</v>
       </c>
-      <c r="D49" s="1">
-        <v>2253993.0118079134</v>
+      <c r="D49" s="2">
+        <v>2244745.808816927</v>
       </c>
       <c r="E49" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B50" s="1" t="s">
@@ -1405,15 +1406,15 @@
       <c r="C50" t="s">
         <v>39</v>
       </c>
-      <c r="D50" s="1">
-        <v>787756.5752191575</v>
+      <c r="D50" s="2">
+        <v>787269.61982345663</v>
       </c>
       <c r="E50" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B51" s="1" t="s">
@@ -1422,15 +1423,15 @@
       <c r="C51" t="s">
         <v>39</v>
       </c>
-      <c r="D51" s="1">
-        <v>721471.14127779554</v>
+      <c r="D51" s="2">
+        <v>720412.62262678379</v>
       </c>
       <c r="E51" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B52" s="1" t="s">
@@ -1439,15 +1440,15 @@
       <c r="C52" t="s">
         <v>39</v>
       </c>
-      <c r="D52" s="1">
-        <v>948528.80917644303</v>
+      <c r="D52" s="2">
+        <v>944856.32358598977</v>
       </c>
       <c r="E52" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B53" s="1" t="s">
@@ -1456,15 +1457,15 @@
       <c r="C53" t="s">
         <v>39</v>
       </c>
-      <c r="D53" s="1">
-        <v>671059.92093134113</v>
+      <c r="D53" s="2">
+        <v>670745.81120777316</v>
       </c>
       <c r="E53" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B54" s="1" t="s">
@@ -1473,15 +1474,15 @@
       <c r="C54" t="s">
         <v>39</v>
       </c>
-      <c r="D54" s="1">
-        <v>264686.49526977632</v>
+      <c r="D54" s="2">
+        <v>263380.99454021611</v>
       </c>
       <c r="E54" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B55" s="1" t="s">
@@ -1490,15 +1491,15 @@
       <c r="C55" t="s">
         <v>39</v>
       </c>
-      <c r="D55" s="1">
-        <v>292635.32834529813</v>
+      <c r="D55" s="2">
+        <v>292085.01389884949</v>
       </c>
       <c r="E55" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B56" s="1" t="s">
@@ -1507,15 +1508,15 @@
       <c r="C56" t="s">
         <v>39</v>
       </c>
-      <c r="D56" s="1">
-        <v>517961.38137721468</v>
+      <c r="D56" s="2">
+        <v>517361.41401338478</v>
       </c>
       <c r="E56" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57" s="2" t="s">
         <v>32</v>
       </c>
       <c r="B57" s="1" t="s">
@@ -1524,15 +1525,15 @@
       <c r="C57" t="s">
         <v>39</v>
       </c>
-      <c r="D57" s="1">
-        <v>963195.22074793931</v>
+      <c r="D57" s="2">
+        <v>963075.97487735341</v>
       </c>
       <c r="E57" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B58" s="1" t="s">
@@ -1541,15 +1542,15 @@
       <c r="C58" t="s">
         <v>39</v>
       </c>
-      <c r="D58" s="1">
-        <v>654054.71904421248</v>
+      <c r="D58" s="2">
+        <v>652483.41067934316</v>
       </c>
       <c r="E58" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A59" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B59" s="1" t="s">
@@ -1558,15 +1559,15 @@
       <c r="C59" t="s">
         <v>39</v>
       </c>
-      <c r="D59" s="1">
-        <v>371524.02773046505</v>
+      <c r="D59" s="2">
+        <v>371397.50574493321</v>
       </c>
       <c r="E59" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A60" s="2" t="s">
         <v>35</v>
       </c>
       <c r="B60" s="1" t="s">
@@ -1575,15 +1576,15 @@
       <c r="C60" t="s">
         <v>39</v>
       </c>
-      <c r="D60" s="1">
+      <c r="D60" s="2">
         <v>625052.52372884739</v>
       </c>
       <c r="E60" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A61" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B61" s="1" t="s">
@@ -1592,15 +1593,15 @@
       <c r="C61" t="s">
         <v>39</v>
       </c>
-      <c r="D61" s="1">
-        <v>977278.28636599006</v>
+      <c r="D61" s="2">
+        <v>977216.55285740539</v>
       </c>
       <c r="E61" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A62" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B62" s="1" t="s">
@@ -1609,15 +1610,15 @@
       <c r="C62" t="s">
         <v>39</v>
       </c>
-      <c r="D62" s="1">
-        <v>1185349.9049153333</v>
+      <c r="D62" s="2">
+        <v>1183806.3265318931</v>
       </c>
       <c r="E62" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A63" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B63" s="1" t="s">
@@ -1626,8 +1627,8 @@
       <c r="C63" t="s">
         <v>39</v>
       </c>
-      <c r="D63" s="1">
-        <v>1455730.3554639828</v>
+      <c r="D63" s="2">
+        <v>1453897.4522929159</v>
       </c>
       <c r="E63" t="s">
         <v>8</v>
@@ -1642,9 +1643,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A389BC6-922E-4815-AF7D-1EE56313E13E}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>40</v>
       </c>
